--- a/mlef_pipeline/results/DCR/HIGH_PDL1/RWD_DP/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/DCR/HIGH_PDL1/RWD_DP/rwd-only/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.68 ± 0.07</t>
+          <t>0.64 ± 0.08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.58 ± 0.04</t>
+          <t>0.55 ± 0.05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.64 ± 0.10</t>
+          <t>0.63 ± 0.17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.57 ± 0.15</t>
+          <t>0.55 ± 0.20</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,17 +498,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.55 ± 0.29</t>
+          <t>0.56 ± 0.27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -528,17 +528,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.78 ± 0.14</t>
+          <t>0.70 ± 0.17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
